--- a/SQL/Templates/entity-students-template.xlsx
+++ b/SQL/Templates/entity-students-template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\PetelFullApp\SQL\Templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A35FD9B7-95FD-40C7-BC30-99FA0876CA99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2473477-5226-4A02-A32A-ABD04CA8A999}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -162,6 +162,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="44" formatCode="_-&quot;₪&quot;* #,##0.00_-;\-&quot;₪&quot;* #,##0.00_-;_-&quot;₪&quot;* &quot;-&quot;??_-;_-@_-"/>
+  </numFmts>
   <fonts count="7">
     <font>
       <sz val="11"/>
@@ -308,9 +311,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -322,7 +322,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="4" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -658,32 +663,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="11"/>
-      <c r="C1" s="11"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
-      <c r="M1" s="11"/>
+      <c r="B1" s="10"/>
+      <c r="C1" s="10"/>
+      <c r="D1" s="10"/>
+      <c r="E1" s="10"/>
+      <c r="F1" s="10"/>
+      <c r="G1" s="10"/>
+      <c r="H1" s="10"/>
+      <c r="I1" s="10"/>
+      <c r="J1" s="10"/>
+      <c r="K1" s="10"/>
+      <c r="L1" s="10"/>
+      <c r="M1" s="10"/>
     </row>
     <row r="2" spans="1:13" ht="6" customHeight="1"/>
     <row r="3" spans="1:13">
       <c r="A3" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="11"/>
+      <c r="C3" s="10"/>
+      <c r="D3" s="10"/>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="1" t="s">
@@ -701,10 +706,10 @@
       <c r="G4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>7</v>
       </c>
-      <c r="I4" s="11"/>
+      <c r="I4" s="10"/>
     </row>
     <row r="5" spans="1:13" ht="6" customHeight="1"/>
     <row r="6" spans="1:13" ht="30" customHeight="1">
@@ -712,25 +717,25 @@
         <v>8</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="C6" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="F6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="G6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="H6" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="3" t="s">
-        <v>13</v>
       </c>
       <c r="I6" s="3" t="s">
         <v>14</v>
@@ -757,26 +762,26 @@
       <c r="A8" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="C8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="D8" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="E8" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="F8" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="G8" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="H8" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="G8" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>27</v>
       </c>
       <c r="I8" s="6" t="s">
         <v>28</v>
@@ -787,10 +792,10 @@
       <c r="K8" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="L8" s="7" t="s">
+      <c r="L8" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="M8" s="7" t="s">
+      <c r="M8" s="12" t="s">
         <v>32</v>
       </c>
     </row>
@@ -800,7 +805,7 @@
       </c>
     </row>
     <row r="10" spans="1:13" ht="17">
-      <c r="K10" s="9" t="s">
+      <c r="K10" s="8" t="s">
         <v>36</v>
       </c>
       <c r="L10" s="13" t="s">
